--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488278_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488278_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5472</v>
+        <v>6.8427</v>
       </c>
       <c r="E2" t="n">
         <v>7.8371</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2899</v>
+        <v>-0.9944</v>
       </c>
       <c r="G2" t="n">
         <v>4.3281</v>
@@ -610,13 +610,13 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6733</v>
+        <v>0.9687</v>
       </c>
       <c r="T2" t="n">
         <v>1.2473</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.574</v>
+        <v>-0.2786</v>
       </c>
       <c r="V2" t="n">
         <v>0.0635</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>J. VARO BARBANCHO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6053</v>
+        <v>4.2739</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1422</v>
+        <v>5.4528</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5369</v>
+        <v>-1.1789</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7197</v>
+        <v>2.2289</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.7706</v>
+        <v>0.2124</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0509</v>
+        <v>2.0165</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8873</v>
+        <v>4.8883</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.108</v>
+        <v>2.2115</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9953</v>
+        <v>2.6768</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.607</v>
+        <v>-2.6594</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6626</v>
+        <v>-1.9991</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9444</v>
+        <v>-0.6603</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6676</v>
+        <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>5.5034</v>
+        <v>0.7781</v>
       </c>
       <c r="T3" t="n">
-        <v>5.1645</v>
+        <v>0.8441</v>
       </c>
       <c r="U3" t="n">
-        <v>0.339</v>
+        <v>-0.0659</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0069</v>
+        <v>1.6374</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9433</v>
+        <v>1.5733</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0635</v>
+        <v>0.0641</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.137</v>
+        <v>2.9344</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6691</v>
+        <v>1.9836</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4679</v>
+        <v>0.9508</v>
       </c>
       <c r="G4" t="n">
         <v>1.4928</v>
@@ -766,13 +766,13 @@
         <v>0.3706</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2742</v>
+        <v>1.0716</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3567</v>
+        <v>0.6712</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9175</v>
+        <v>0.4004</v>
       </c>
       <c r="V4" t="n">
         <v>-0.0005</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VARO BARBANCHO</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2644</v>
+        <v>1.602</v>
       </c>
       <c r="E5" t="n">
-        <v>3.788</v>
+        <v>2.3479</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5236</v>
+        <v>-0.746</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2289</v>
+        <v>1.7866</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2124</v>
+        <v>1.2274</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0165</v>
+        <v>0.5592</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8883</v>
+        <v>2.1227</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2115</v>
+        <v>2.0398</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6768</v>
+        <v>0.0829</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.6594</v>
+        <v>-0.3361</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9991</v>
+        <v>-0.8124</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6603</v>
+        <v>0.4763</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4823</v>
+        <v>0.7411</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2314</v>
+        <v>-0.2969</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8207</v>
+        <v>-0.0892</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4106</v>
+        <v>-0.2077</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6374</v>
+        <v>-0.6289</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5733</v>
+        <v>0.3144</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0641</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2836</v>
+        <v>1.4951</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0542</v>
+        <v>2.2043</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7706</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7866</v>
+        <v>-1.7197</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2274</v>
+        <v>-1.7706</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5592</v>
+        <v>0.0509</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1227</v>
+        <v>0.8873</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0398</v>
+        <v>-0.108</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0829</v>
+        <v>0.9953</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3361</v>
+        <v>-2.607</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8124</v>
+        <v>-1.6626</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4763</v>
+        <v>-0.9444</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7411</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6153</v>
+        <v>2.3932</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.383</v>
+        <v>2.2266</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2323</v>
+        <v>0.1666</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6289</v>
+        <v>1.0069</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>0.9433</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.9433</v>
+        <v>0.0635</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2162</v>
+        <v>-0.1669</v>
       </c>
       <c r="E7" t="n">
         <v>0.0664</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2826</v>
+        <v>-0.2333</v>
       </c>
       <c r="G7" t="n">
         <v>-0.586</v>
@@ -1000,13 +1000,13 @@
         <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1845</v>
+        <v>0.2338</v>
       </c>
       <c r="T7" t="n">
         <v>0.2699</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0853</v>
+        <v>-0.0361</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2932</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5331</v>
+        <v>-0.1524</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8263</v>
+        <v>-0.8017</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6921</v>
@@ -1078,13 +1078,13 @@
         <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>1.158</v>
+        <v>0.4971</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1416</v>
+        <v>0.4561</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9444</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4188</v>
+        <v>-1.2716</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0098</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.409</v>
+        <v>-0.3598</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1008</v>
@@ -1156,13 +1156,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2619</v>
+        <v>-0.1147</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1641</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V9" t="n">
         <v>0.3144</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4999</v>
+        <v>-1.6426</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9409</v>
+        <v>1.7244</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4408</v>
+        <v>-3.367</v>
       </c>
       <c r="G10" t="n">
         <v>-0.31</v>
@@ -1234,13 +1234,13 @@
         <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0602</v>
+        <v>0.7971</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2773</v>
+        <v>0.5061</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2171</v>
+        <v>0.291</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5738</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.9432</v>
+        <v>-5.8173</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3587</v>
+        <v>-3.1835</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5845</v>
+        <v>-2.6337</v>
       </c>
       <c r="G11" t="n">
         <v>-6.046</v>
@@ -1312,13 +1312,13 @@
         <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0219</v>
+        <v>1.1478</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1131</v>
+        <v>1.062</v>
       </c>
       <c r="U11" t="n">
-        <v>0.135</v>
+        <v>0.0858</v>
       </c>
       <c r="V11" t="n">
         <v>0.378</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.8542</v>
+        <v>-7.6835</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4885</v>
+        <v>-3.1947</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.3657</v>
+        <v>-4.4888</v>
       </c>
       <c r="G12" t="n">
         <v>-5.3312</v>
@@ -1390,13 +1390,13 @@
         <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.2528</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0037</v>
+        <v>0.2901</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0858</v>
+        <v>-0.0373</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5669999999999999</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3880000000000017</v>
+        <v>-0.3878999999999992</v>
       </c>
       <c r="E13" t="n">
-        <v>14.174</v>
+        <v>14.1741</v>
       </c>
       <c r="F13" t="n">
         <v>-14.562</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.9494</v>
+        <v>-5.949399999999998</v>
       </c>
       <c r="H13" t="n">
         <v>-5.4114</v>
@@ -1468,13 +1468,13 @@
         <v>10.1908</v>
       </c>
       <c r="S13" t="n">
-        <v>7.728599999999999</v>
+        <v>7.728600000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>7.4181</v>
+        <v>7.417999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3109</v>
+        <v>0.3106999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3144000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.86</v>
+        <v>6.6932</v>
       </c>
       <c r="E14" t="n">
-        <v>7.9882</v>
+        <v>8.6737</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1282</v>
+        <v>-1.9804</v>
       </c>
       <c r="G14" t="n">
         <v>6.9198</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1884</v>
+        <v>-1.3552</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.149</v>
+        <v>-0.4635</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0394</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0.9433</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6015</v>
+        <v>1.6312</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7832</v>
+        <v>4.5666</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.1816</v>
+        <v>-2.9354</v>
       </c>
       <c r="G16" t="n">
         <v>4.1808</v>
@@ -1702,13 +1702,13 @@
         <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.5057</v>
+        <v>-1.4761</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2584</v>
+        <v>-0.475</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2473</v>
+        <v>-1.0011</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2589</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4995</v>
+        <v>0.3987</v>
       </c>
       <c r="E17" t="n">
-        <v>1.022</v>
+        <v>1.6386</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5226</v>
+        <v>-1.2398</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.248</v>
+        <v>-0.2496</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0086</v>
+        <v>2.363</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2394</v>
+        <v>-2.6127</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1695</v>
+        <v>2.1652</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1208</v>
+        <v>3.2422</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2903</v>
+        <v>-1.077</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4175</v>
+        <v>-2.4148</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8878</v>
+        <v>-0.8791</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-1.5357</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1117</v>
+        <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9513</v>
+        <v>-1.4257</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5397</v>
+        <v>-0.5614</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4116</v>
+        <v>-0.8643</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3155</v>
+        <v>1.8888</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3128</v>
+        <v>1.8877</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6283</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1888</v>
+        <v>-0.0165</v>
       </c>
       <c r="E18" t="n">
-        <v>1.051</v>
+        <v>1.5492</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2398</v>
+        <v>-1.5657</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2496</v>
+        <v>-0.0392</v>
       </c>
       <c r="H18" t="n">
-        <v>2.363</v>
+        <v>0.6227</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6127</v>
+        <v>-0.6619</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1652</v>
+        <v>0.9116</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2422</v>
+        <v>0.8287</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.077</v>
+        <v>0.0829</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.4148</v>
+        <v>-0.9508</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8791</v>
+        <v>-0.206</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5357</v>
+        <v>-0.7448</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0382</v>
+        <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.0133</v>
+        <v>-0.4601</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.149</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8643</v>
+        <v>-0.4688</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8888</v>
+        <v>-0.6289</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8877</v>
+        <v>0.6289</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0011</v>
+        <v>-1.2578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4194</v>
+        <v>-0.2974</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1654</v>
+        <v>0.3612</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5848</v>
+        <v>-0.6587</v>
       </c>
       <c r="G19" t="n">
         <v>0.3608</v>
@@ -1936,13 +1936,13 @@
         <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8538</v>
+        <v>-0.7318</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0584</v>
+        <v>0.1374</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7954</v>
+        <v>-0.8693</v>
       </c>
       <c r="V19" t="n">
         <v>0.6294</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>N. RAMIREZ PRIETO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4328</v>
+        <v>-0.3124</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1575</v>
+        <v>0.1906</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5903</v>
+        <v>-0.503</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0392</v>
+        <v>-0.0522</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6227</v>
+        <v>0.4561</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6619</v>
+        <v>-0.5083</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9116</v>
+        <v>0.1474</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8287</v>
+        <v>0.0644</v>
       </c>
       <c r="L20" t="n">
         <v>0.0829</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9508</v>
+        <v>-0.1996</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.206</v>
+        <v>0.3917</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7448</v>
+        <v>-0.5913</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8764</v>
+        <v>-0.4455</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.383</v>
+        <v>0.0432</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4934</v>
+        <v>-0.4887</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. RAMIREZ PRIETO</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5088</v>
+        <v>-0.6785</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0926</v>
+        <v>0.3365</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6015</v>
+        <v>-1.015</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0522</v>
+        <v>-1.248</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4561</v>
+        <v>-1.0086</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5083</v>
+        <v>-0.2394</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1474</v>
+        <v>0.1695</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0644</v>
+        <v>-0.1208</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0829</v>
+        <v>0.2903</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1996</v>
+        <v>-1.4175</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3917</v>
+        <v>-0.8878</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5913</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6419</v>
+        <v>-0.2266</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0547</v>
+        <v>-0.1458</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.0809</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3128</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6283</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0964</v>
+        <v>-1.9296</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1161</v>
+        <v>-1.8016</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0197</v>
+        <v>-0.128</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9791</v>
@@ -2170,13 +2170,13 @@
         <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5121</v>
+        <v>-0.3211</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7039</v>
+        <v>0.0184</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1918</v>
+        <v>-0.3395</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4326</v>
+        <v>-2.3534</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8902</v>
+        <v>-0.6867</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3228</v>
+        <v>-1.6667</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8798</v>
+        <v>-1.8862</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.29</v>
+        <v>-0.3563</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4102</v>
+        <v>-1.5299</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7616000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.524</v>
+        <v>1.138</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2856</v>
+        <v>-1.2228</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6414</v>
+        <v>-1.8014</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.766</v>
+        <v>-1.4943</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8754</v>
+        <v>-0.3071</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7060999999999999</v>
+        <v>-0.5969</v>
       </c>
       <c r="T23" t="n">
-        <v>1.685</v>
+        <v>0.3246</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9789</v>
+        <v>-0.9215</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2589</v>
+        <v>0.315</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6289</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.255</v>
+        <v>-2.4263</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.659</v>
+        <v>-1.8549</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.596</v>
+        <v>-0.5714</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3662</v>
@@ -2326,13 +2326,13 @@
         <v>0.1853</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1477</v>
+        <v>-0.319</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4887</v>
+        <v>0.2929</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6364</v>
+        <v>-0.6118</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4273</v>
+        <v>-2.5093</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6867</v>
+        <v>-0.285</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7406</v>
+        <v>-2.2243</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.8862</v>
+        <v>-0.8798</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3563</v>
+        <v>-1.29</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.5299</v>
+        <v>0.4102</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0848</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>1.138</v>
+        <v>-0.524</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2228</v>
+        <v>1.2856</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8014</v>
+        <v>-1.6414</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4943</v>
+        <v>-0.766</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3071</v>
+        <v>-0.8754</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6708</v>
+        <v>-0.3706</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3246</v>
+        <v>0.5099</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9953</v>
+        <v>-0.8804</v>
       </c>
       <c r="V25" t="n">
-        <v>0.315</v>
+        <v>-1.2589</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X25" t="n">
-        <v>0.315</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="26">
@@ -2437,22 +2437,22 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3882000000000012</v>
+        <v>0.387999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>14.8766</v>
+        <v>14.8765</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.4885</v>
+        <v>-14.4884</v>
       </c>
       <c r="G26" t="n">
-        <v>5.949400000000001</v>
+        <v>5.949399999999999</v>
       </c>
       <c r="H26" t="n">
         <v>5.4113</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5378999999999992</v>
+        <v>0.5379000000000005</v>
       </c>
       <c r="J26" t="n">
         <v>20.6627</v>
@@ -2461,7 +2461,7 @@
         <v>13.6371</v>
       </c>
       <c r="L26" t="n">
-        <v>7.025499999999998</v>
+        <v>7.025499999999999</v>
       </c>
       <c r="M26" t="n">
         <v>-14.7132</v>
@@ -2482,22 +2482,22 @@
         <v>12.0437</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.728499999999999</v>
+        <v>-7.728599999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3106000000000003</v>
+        <v>-0.3106</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.417800000000001</v>
+        <v>-7.417899999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3143000000000005</v>
+        <v>0.3143</v>
       </c>
       <c r="W26" t="n">
         <v>4.7155</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.401099999999999</v>
+        <v>-4.4011</v>
       </c>
     </row>
   </sheetData>
